--- a/docs/business/tech-budget-3y.xlsx
+++ b/docs/business/tech-budget-3y.xlsx
@@ -1,18 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="الملخّص" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="الفرضيات" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="البنية التحتية" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="الذكاء الاصطناعي" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="الفريق التقني" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="الأمن والأدوات" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الفرضيات" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="البنية التحتية" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الذكاء الاصطناعي" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الفريق التقني" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الأمن والأدوات" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الملخّص" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="النموذج المالي" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="خارطة الطريق" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="طلب التمويل" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,10 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.0&quot; ر.س&quot;"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00&quot; ر.س&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,6 +71,11 @@
       <b val="1"/>
       <color rgb="00A8792F"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="005B2C87"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -118,17 +127,33 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -146,22 +171,24 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,289 +554,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>الملخّص التنفيذي — التكلفة التشغيلية التقنية (ريال)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>البند</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>السنة 1</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>السنة 2</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>السنة 3</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>الإجمالي</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>البنية التحتية</t>
-        </is>
-      </c>
-      <c r="B4" s="4">
-        <f>'البنية التحتية'!B12</f>
-        <v/>
-      </c>
-      <c r="C4" s="4">
-        <f>'البنية التحتية'!C12</f>
-        <v/>
-      </c>
-      <c r="D4" s="4">
-        <f>'البنية التحتية'!D12</f>
-        <v/>
-      </c>
-      <c r="E4" s="4">
-        <f>SUM(B4:D4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>الذكاء الاصطناعي</t>
-        </is>
-      </c>
-      <c r="B5" s="4">
-        <f>'الذكاء الاصطناعي'!B8</f>
-        <v/>
-      </c>
-      <c r="C5" s="4">
-        <f>'الذكاء الاصطناعي'!C8</f>
-        <v/>
-      </c>
-      <c r="D5" s="4">
-        <f>'الذكاء الاصطناعي'!D8</f>
-        <v/>
-      </c>
-      <c r="E5" s="4">
-        <f>SUM(B5:D5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>الفريق التقني</t>
-        </is>
-      </c>
-      <c r="B6" s="4">
-        <f>'الفريق التقني'!D8</f>
-        <v/>
-      </c>
-      <c r="C6" s="4">
-        <f>'الفريق التقني'!E8</f>
-        <v/>
-      </c>
-      <c r="D6" s="4">
-        <f>'الفريق التقني'!F8</f>
-        <v/>
-      </c>
-      <c r="E6" s="4">
-        <f>SUM(B6:D6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>الأمن والأدوات</t>
-        </is>
-      </c>
-      <c r="B7" s="4">
-        <f>'الأمن والأدوات'!B8</f>
-        <v/>
-      </c>
-      <c r="C7" s="4">
-        <f>'الأمن والأدوات'!C8</f>
-        <v/>
-      </c>
-      <c r="D7" s="4">
-        <f>'الأمن والأدوات'!D8</f>
-        <v/>
-      </c>
-      <c r="E7" s="4">
-        <f>SUM(B7:D7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>احتياطي طوارئ 10٪</t>
-        </is>
-      </c>
-      <c r="B8" s="4">
-        <f>SUM(B4:B7)*$B$16</f>
-        <v/>
-      </c>
-      <c r="C8" s="4">
-        <f>SUM(C4:C7)*$B$16</f>
-        <v/>
-      </c>
-      <c r="D8" s="4">
-        <f>SUM(D4:D7)*$B$16</f>
-        <v/>
-      </c>
-      <c r="E8" s="4">
-        <f>SUM(B8:D8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>الإجمالي النهائي</t>
-        </is>
-      </c>
-      <c r="B9" s="6">
-        <f>SUM(B4:B8)</f>
-        <v/>
-      </c>
-      <c r="C9" s="6">
-        <f>SUM(C4:C8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="6">
-        <f>SUM(D4:D8)</f>
-        <v/>
-      </c>
-      <c r="E9" s="6">
-        <f>SUM(B9:D9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>الأطروحة الاستثمارية</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>المؤشّر</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>السنة 1</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>السنة 2</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>السنة 3</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>الرحلات سنويًّا</t>
-        </is>
-      </c>
-      <c r="B13" s="4">
-        <f>الفرضيات!B7</f>
-        <v/>
-      </c>
-      <c r="C13" s="4">
-        <f>الفرضيات!C7</f>
-        <v/>
-      </c>
-      <c r="D13" s="4">
-        <f>الفرضيات!D7</f>
-        <v/>
-      </c>
-      <c r="E13" s="4" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>التكلفة التقنية لكل رحلة</t>
-        </is>
-      </c>
-      <c r="B14" s="9">
-        <f>B9/B13</f>
-        <v/>
-      </c>
-      <c r="C14" s="9">
-        <f>C9/C13</f>
-        <v/>
-      </c>
-      <c r="D14" s="9">
-        <f>D9/D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="10" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>نسبة احتياطي الطوارئ</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>بنود خارج هذه الوثيقة: رسوم بوّابة الدفع · ترخيص هيئة النقل · التسويق واكتساب المستخدمات · حوافز السائقات · المقرّ والإداريّون.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -849,71 +593,71 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>المدن المغطّاة</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="4" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>مستخدمات نشطات شهريًّا</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="4" t="n">
         <v>5000</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="4" t="n">
         <v>35000</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="4" t="n">
         <v>120000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>سائقات نشطات</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="4" t="n">
         <v>1200</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="4" t="n">
         <v>4000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>الرحلات سنويًّا</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="4" t="n">
         <v>30000</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="4" t="n">
         <v>300000</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="4" t="n">
         <v>1000000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>الخلايا الذهبية = مدخلات قابلة للتعديل. الباقي في الأوراق الأخرى محسوب بصيغ.</t>
         </is>
@@ -927,7 +671,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -972,148 +716,148 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Supabase — قاعدة البيانات والمصادقة والتخزين</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="4" t="n">
         <v>2250</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="4" t="n">
         <v>11250</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="4" t="n">
         <v>34000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Vercel — لوحة الإدارة وصفحة الهبوط</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="4" t="n">
         <v>900</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="4" t="n">
         <v>2250</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="4" t="n">
         <v>4500</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Mapbox — الخرائط وحساب المسارات</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="4" t="n">
         <v>5600</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="4" t="n">
         <v>45000</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="4" t="n">
         <v>135000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Expo EAS — البناء والتحديث الفوري</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="4" t="n">
         <v>4500</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="4" t="n">
         <v>4500</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="4" t="n">
         <v>9000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>رسائل التحقّق (~0.15 ريال/رسالة)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="4" t="n">
         <v>3000</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="4" t="n">
         <v>22500</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="4" t="n">
         <v>75000</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>المراقبة وتتبّع الأعطال</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="4" t="n">
         <v>1200</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="4" t="n">
         <v>2500</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="4" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>متاجر التطبيقات والنطاق</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="4" t="n">
         <v>700</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="4" t="n">
         <v>500</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="4" t="n">
         <v>500</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>النسخ الاحتياطي والتعافي</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
+      <c r="B11" s="4" t="n">
         <v>2000</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="4" t="n">
         <v>5000</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="4" t="n">
         <v>10000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="7">
         <f>SUM(B4:B11)</f>
         <v/>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="7">
         <f>SUM(C4:C11)</f>
         <v/>
       </c>
-      <c r="D12" s="16">
+      <c r="D12" s="7">
         <f>SUM(D4:D11)</f>
         <v/>
       </c>
@@ -1126,7 +870,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1171,84 +915,84 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>استدعاءات النماذج اللغوية — مخطّط الرحلات والدعم</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="4" t="n">
         <v>2250</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="4" t="n">
         <v>15000</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="4" t="n">
         <v>45000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>تدريب نموذج خاص (ضبط دقيق)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="4" t="n">
         <v>56000</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="4" t="n">
         <v>112000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>وسم البيانات وإعدادها</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="4" t="n">
         <v>20000</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="4" t="n">
         <v>35000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>نماذج التنبّؤ — الطلب والتسعير والمطابقة</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="4" t="n">
         <v>25000</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="4" t="n">
         <v>55000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="7">
         <f>SUM(B4:B7)</f>
         <v/>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="7">
         <f>SUM(C4:C7)</f>
         <v/>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="7">
         <f>SUM(D4:D7)</f>
         <v/>
       </c>
@@ -1261,7 +1005,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1318,141 +1062,141 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>قائد تقني (CTO)</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="4" t="n">
         <v>18000</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="8">
         <f>$B4*12*$C4*$B$11</f>
         <v/>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="8">
         <f>D4*(1+$B$12)</f>
         <v/>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="8">
         <f>E4*(1+$B$12)</f>
         <v/>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>مطوّر تقني (Full-stack)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="4" t="n">
         <v>13000</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="8">
         <f>$B5*12*$C5*$B$11</f>
         <v/>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="8">
         <f>D5*(1+$B$12)</f>
         <v/>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="8">
         <f>E5*(1+$B$12)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>مطوّر تقني مساعد</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="4" t="n">
         <v>8000</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="8">
         <f>$B6*12*$C6*$B$11</f>
         <v/>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="8">
         <f>D6*(1+$B$12)</f>
         <v/>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="8">
         <f>E6*(1+$B$12)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>دعم فنّي</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="4" t="n">
         <v>6000</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="8">
         <f>$B7*12*$C7*$B$11</f>
         <v/>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="8">
         <f>D7*(1+$B$12)</f>
         <v/>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="8">
         <f>E7*(1+$B$12)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="B8" s="16" t="inlineStr"/>
-      <c r="C8" s="16">
+      <c r="B8" s="7" t="inlineStr"/>
+      <c r="C8" s="7">
         <f>SUM(C4:C7)</f>
         <v/>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="7">
         <f>SUM(D4:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="7">
         <f>SUM(E4:E7)</f>
         <v/>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="7">
         <f>SUM(F4:F7)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>معامل أعباء التوظيف</t>
         </is>
       </c>
-      <c r="B11" s="18" t="n">
+      <c r="B11" s="10" t="n">
         <v>1.2</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>الزيادة السنوية</t>
         </is>
@@ -1462,7 +1206,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>فريق ثابت عبر السنوات الثلاث — دور واحد لكل تخصّص جوهري. ممكن لأنّ البنية تعتمد خدمات سحابية مُدارة، فلا حاجة لفريق تشغيل خوادم.</t>
         </is>
@@ -1476,7 +1220,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1521,84 +1265,84 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>اختبار اختراق ومراجعة أمنية</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="4" t="n">
         <v>30000</v>
       </c>
-      <c r="C4" s="14" t="n">
+      <c r="C4" s="4" t="n">
         <v>30000</v>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="4" t="n">
         <v>45000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>الامتثال لنظام حماية البيانات الشخصية</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="4" t="n">
         <v>25000</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="4" t="n">
         <v>15000</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="4" t="n">
         <v>20000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>تراخيص الأدوات وبيئة العمل</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="4" t="n">
         <v>15000</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="4" t="n">
         <v>35000</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="4" t="n">
         <v>60000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>أجهزة الفريق</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
+      <c r="B7" s="4" t="n">
         <v>50000</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="4" t="n">
         <v>35000</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="4" t="n">
         <v>50000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>الإجمالي</t>
         </is>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="7">
         <f>SUM(B4:B7)</f>
         <v/>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="7">
         <f>SUM(C4:C7)</f>
         <v/>
       </c>
-      <c r="D8" s="16">
+      <c r="D8" s="7">
         <f>SUM(D4:D7)</f>
         <v/>
       </c>
@@ -1609,4 +1353,930 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>الملخّص التنفيذي — التكلفة التشغيلية التقنية (ريال)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>البند</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>السنة 1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>السنة 2</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>السنة 3</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>الإجمالي</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>البنية التحتية</t>
+        </is>
+      </c>
+      <c r="B4" s="8">
+        <f>'البنية التحتية'!B12</f>
+        <v/>
+      </c>
+      <c r="C4" s="8">
+        <f>'البنية التحتية'!C12</f>
+        <v/>
+      </c>
+      <c r="D4" s="8">
+        <f>'البنية التحتية'!D12</f>
+        <v/>
+      </c>
+      <c r="E4" s="8">
+        <f>SUM(B4:D4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>الذكاء الاصطناعي</t>
+        </is>
+      </c>
+      <c r="B5" s="8">
+        <f>'الذكاء الاصطناعي'!B8</f>
+        <v/>
+      </c>
+      <c r="C5" s="8">
+        <f>'الذكاء الاصطناعي'!C8</f>
+        <v/>
+      </c>
+      <c r="D5" s="8">
+        <f>'الذكاء الاصطناعي'!D8</f>
+        <v/>
+      </c>
+      <c r="E5" s="8">
+        <f>SUM(B5:D5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>الفريق التقني</t>
+        </is>
+      </c>
+      <c r="B6" s="8">
+        <f>'الفريق التقني'!D8</f>
+        <v/>
+      </c>
+      <c r="C6" s="8">
+        <f>'الفريق التقني'!E8</f>
+        <v/>
+      </c>
+      <c r="D6" s="8">
+        <f>'الفريق التقني'!F8</f>
+        <v/>
+      </c>
+      <c r="E6" s="8">
+        <f>SUM(B6:D6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>الأمن والأدوات</t>
+        </is>
+      </c>
+      <c r="B7" s="8">
+        <f>'الأمن والأدوات'!B8</f>
+        <v/>
+      </c>
+      <c r="C7" s="8">
+        <f>'الأمن والأدوات'!C8</f>
+        <v/>
+      </c>
+      <c r="D7" s="8">
+        <f>'الأمن والأدوات'!D8</f>
+        <v/>
+      </c>
+      <c r="E7" s="8">
+        <f>SUM(B7:D7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>احتياطي طوارئ 10٪</t>
+        </is>
+      </c>
+      <c r="B8" s="8">
+        <f>SUM(B4:B7)*$B$16</f>
+        <v/>
+      </c>
+      <c r="C8" s="8">
+        <f>SUM(C4:C7)*$B$16</f>
+        <v/>
+      </c>
+      <c r="D8" s="8">
+        <f>SUM(D4:D7)*$B$16</f>
+        <v/>
+      </c>
+      <c r="E8" s="8">
+        <f>SUM(B8:D8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>الإجمالي النهائي</t>
+        </is>
+      </c>
+      <c r="B9" s="14">
+        <f>SUM(B4:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="14">
+        <f>SUM(C4:C8)</f>
+        <v/>
+      </c>
+      <c r="D9" s="14">
+        <f>SUM(D4:D8)</f>
+        <v/>
+      </c>
+      <c r="E9" s="14">
+        <f>SUM(B9:D9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>الأطروحة الاستثمارية</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>المؤشّر</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>السنة 1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>السنة 2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>السنة 3</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>الرحلات سنويًّا</t>
+        </is>
+      </c>
+      <c r="B13" s="8">
+        <f>الفرضيات!B7</f>
+        <v/>
+      </c>
+      <c r="C13" s="8">
+        <f>الفرضيات!C7</f>
+        <v/>
+      </c>
+      <c r="D13" s="8">
+        <f>الفرضيات!D7</f>
+        <v/>
+      </c>
+      <c r="E13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>التكلفة التقنية لكل رحلة</t>
+        </is>
+      </c>
+      <c r="B14" s="17">
+        <f>B9/B13</f>
+        <v/>
+      </c>
+      <c r="C14" s="17">
+        <f>C9/C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="17">
+        <f>D9/D13</f>
+        <v/>
+      </c>
+      <c r="E14" s="18" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>نسبة احتياطي الطوارئ</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>بنود خارج هذه الوثيقة: رسوم بوّابة الدفع · ترخيص هيئة النقل · التسويق واكتساب المستخدمات · حوافز السائقات · المقرّ والإداريّون.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>التوقّعات المالية — الإيراد من عمولة الرحلات (ريال)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>المؤشّر</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>السنة 1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>السنة 2</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>السنة 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>الرحلات سنويًّا</t>
+        </is>
+      </c>
+      <c r="B4" s="8">
+        <f>الفرضيات!B7</f>
+        <v/>
+      </c>
+      <c r="C4" s="8">
+        <f>الفرضيات!C7</f>
+        <v/>
+      </c>
+      <c r="D4" s="8">
+        <f>الفرضيات!D7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>متوسّط قيمة الرحلة</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>نسبة عمولة المنصّة</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>إجمالي قيمة الرحلات (GMV)</t>
+        </is>
+      </c>
+      <c r="B8" s="8">
+        <f>B4*$B$5</f>
+        <v/>
+      </c>
+      <c r="C8" s="8">
+        <f>C4*$B$5</f>
+        <v/>
+      </c>
+      <c r="D8" s="8">
+        <f>D4*$B$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>عمولة المنصّة</t>
+        </is>
+      </c>
+      <c r="B9" s="8">
+        <f>B8*$B$6</f>
+        <v/>
+      </c>
+      <c r="C9" s="8">
+        <f>C8*$B$6</f>
+        <v/>
+      </c>
+      <c r="D9" s="8">
+        <f>D8*$B$6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>اشتراكات وإعلانات</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>إجمالي الإيرادات</t>
+        </is>
+      </c>
+      <c r="B11" s="7">
+        <f>B9+B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="7">
+        <f>C9+C10</f>
+        <v/>
+      </c>
+      <c r="D11" s="7">
+        <f>D9+D10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>التكلفة التقنية</t>
+        </is>
+      </c>
+      <c r="B13" s="8">
+        <f>'الملخّص'!B9</f>
+        <v/>
+      </c>
+      <c r="C13" s="8">
+        <f>'الملخّص'!C9</f>
+        <v/>
+      </c>
+      <c r="D13" s="8">
+        <f>'الملخّص'!D9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>التشغيل والتسويق والإدارة</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>521360</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>1048550</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>2148500</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>إجمالي التكاليف</t>
+        </is>
+      </c>
+      <c r="B15" s="7">
+        <f>B13+B14</f>
+        <v/>
+      </c>
+      <c r="C15" s="7">
+        <f>C13+C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="7">
+        <f>D13+D14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>صافي الربح / (الخسارة)</t>
+        </is>
+      </c>
+      <c r="B17" s="19">
+        <f>B11-B15</f>
+        <v/>
+      </c>
+      <c r="C17" s="19">
+        <f>C11-C15</f>
+        <v/>
+      </c>
+      <c r="D17" s="19">
+        <f>D11-D15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>الصافي التراكمي</t>
+        </is>
+      </c>
+      <c r="B18" s="20">
+        <f>B17</f>
+        <v/>
+      </c>
+      <c r="C18" s="20">
+        <f>B18+C17</f>
+        <v/>
+      </c>
+      <c r="D18" s="20">
+        <f>C18+D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>إيراد الرحلة الواحدة</t>
+        </is>
+      </c>
+      <c r="B20" s="21">
+        <f>B11/B4</f>
+        <v/>
+      </c>
+      <c r="C20" s="21">
+        <f>C11/C4</f>
+        <v/>
+      </c>
+      <c r="D20" s="21">
+        <f>D11/D4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>تكلفة الرحلة الواحدة</t>
+        </is>
+      </c>
+      <c r="B21" s="21">
+        <f>B15/B4</f>
+        <v/>
+      </c>
+      <c r="C21" s="21">
+        <f>C15/C4</f>
+        <v/>
+      </c>
+      <c r="D21" s="21">
+        <f>D15/D4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>هامش المساهمة للرحلة</t>
+        </is>
+      </c>
+      <c r="B22" s="22">
+        <f>B20-B21</f>
+        <v/>
+      </c>
+      <c r="C22" s="22">
+        <f>C20-C21</f>
+        <v/>
+      </c>
+      <c r="D22" s="22">
+        <f>D20-D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>نقطة التعادل في السنة الثانية، والربحية الكاملة في السنة الثالثة. الخسارة في السنة الأولى كلفة بناء شبكة السائقات وقاعدة المستخدمات.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>خارطة الطريق — رأس المال التأسيسي (ريال)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>الشهر</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>المرحلة</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>الأنشطة الرئيسية</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>التكلفة</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>1 – 2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>التأسيس والترخيص الريادي</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>خطاب تأييد جامعة القصيم، الترخيص، السجل التجاري</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>2 – 4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>التطوير التقني (MVP)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>بناء التطبيقات، تكامل الخرائط والدفع، البنية السحابية</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>التوظيف والتدريب</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>استقطاب أوّل 100 سائقة وتأهيلهنّ</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>الإطلاق التجريبي</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>التشغيل في بريدة وجمع الملاحظات الميدانية</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>الإطلاق الرسمي</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>حملة تسويقية واستقطاب 5 آلاف مستخدمة</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>التوسّع الإقليمي</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>الرياض وجدة والدمام</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr"/>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>الإجمالي</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr"/>
+      <c r="D10" s="7">
+        <f>SUM(D4:D9)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>أوجه استخدام التمويل المطلوب (ريال)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>البند</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>المبلغ</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>النسبة</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>التطوير التقني والبنية التحتية</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>1280000</v>
+      </c>
+      <c r="C4" s="23">
+        <f>B4/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>التسويق واكتساب المستخدمات</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>650000</v>
+      </c>
+      <c r="C5" s="23">
+        <f>B5/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>استقطاب السائقات وتأهيلهنّ</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>320000</v>
+      </c>
+      <c r="C6" s="23">
+        <f>B6/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>التراخيص والامتثال القانوني</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>125000</v>
+      </c>
+      <c r="C7" s="23">
+        <f>B7/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>احتياطي تشغيلي</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>125000</v>
+      </c>
+      <c r="C8" s="23">
+        <f>B8/$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>الإجمالي</t>
+        </is>
+      </c>
+      <c r="B9" s="7">
+        <f>SUM(B4:B8)</f>
+        <v/>
+      </c>
+      <c r="C9" s="24">
+        <f>SUM(C4:C8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>يغطّي رأس المال التأسيسي وعجز التشغيل حتى نقطة التعادل في السنة الثانية، مع هامش أمان. مصادر مستهدفة: منشآت · كفالة · ريادة · رواد التقنية · حاضنة جامعة القصيم.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>